--- a/PreTest_credentials.xlsx
+++ b/PreTest_credentials.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Jag\harman_training\Training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7B27B5A7-8F4E-4403-BE67-136ADC4C98E0}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CF3B37D-66D4-409D-B6F4-CEE3C15638B2}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{2B36BAF6-5AD8-42C4-A2BB-D8862FC6E603}"/>
   </bookViews>
@@ -761,10 +761,10 @@
         <v>12</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -778,10 +778,10 @@
         <v>15</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -795,10 +795,10 @@
         <v>18</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -812,10 +812,10 @@
         <v>21</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -829,10 +829,10 @@
         <v>24</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -846,10 +846,10 @@
         <v>27</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -863,10 +863,10 @@
         <v>30</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -880,10 +880,10 @@
         <v>33</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -897,10 +897,10 @@
         <v>36</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -914,10 +914,10 @@
         <v>39</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -931,10 +931,10 @@
         <v>42</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -948,10 +948,10 @@
         <v>45</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -965,10 +965,10 @@
         <v>48</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -982,10 +982,10 @@
         <v>51</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -999,10 +999,10 @@
         <v>54</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1016,10 +1016,10 @@
         <v>57</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1033,37 +1033,39 @@
         <v>60</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B24" s="1"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="6"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E5" r:id="rId1" display="mailto:madhusudhana.vemula@harman.com" xr:uid="{E51556A3-7AF6-4987-B92A-7F9FACDC10A8}"/>
     <hyperlink ref="F5" r:id="rId2" display="mailto:madhusudhana.vemula@harman.com" xr:uid="{E99D62EB-C4C8-4FBA-8AF3-68D115FE5081}"/>
     <hyperlink ref="E6" r:id="rId3" display="mailto:pratap.narayan@harman.com" xr:uid="{F389F03E-94C5-48A6-8F6C-703C852DEE1A}"/>
-    <hyperlink ref="E7" r:id="rId4" display="mailto:gayatri.behera@harman.com" xr:uid="{21679528-AA71-4DE8-A4C0-D26B371344C7}"/>
-    <hyperlink ref="E8" r:id="rId5" display="mailto:kamran.siddiqui@harman.com" xr:uid="{B4354F16-B160-42FD-90B0-773FFAFA69F9}"/>
-    <hyperlink ref="E9" r:id="rId6" display="mailto:lalitha.saripalli@harman.com" xr:uid="{03B684BE-B201-4FAE-B650-8FE522DBB3A6}"/>
-    <hyperlink ref="E10" r:id="rId7" display="mailto:megha.kesharwani@harman.com" xr:uid="{11BC7E09-4E5B-4D32-84CC-8DC44E062A95}"/>
-    <hyperlink ref="E11" r:id="rId8" display="mailto:vaishnavi.ballal@harman.com" xr:uid="{C2A05FE7-4633-4420-92C8-D7E30C037435}"/>
-    <hyperlink ref="E12" r:id="rId9" display="mailto:rasmita.parida@harman.com" xr:uid="{2EC03D2C-4EB5-420F-A2AE-1CEBFA499E3E}"/>
-    <hyperlink ref="E13" r:id="rId10" display="mailto:varsha.gadekar@harman.com" xr:uid="{F317EFCD-459E-4968-8854-69713133520F}"/>
-    <hyperlink ref="E14" r:id="rId11" display="mailto:shunmuga.priya@harman.com" xr:uid="{735A5AAF-2FAB-4830-9EFE-E842143C12DD}"/>
-    <hyperlink ref="E15" r:id="rId12" display="mailto:sunkara.hussain@harman.com" xr:uid="{D8618987-6C7D-4B82-AC18-995F3E744827}"/>
-    <hyperlink ref="E16" r:id="rId13" display="mailto:hruthkarsha.ds@harman.com" xr:uid="{FC493C81-C249-4752-8703-861C7E251077}"/>
-    <hyperlink ref="E17" r:id="rId14" display="mailto:harshitha.v@harman.com" xr:uid="{DE50E738-2396-40D7-8B9C-ABCE851B9A6D}"/>
-    <hyperlink ref="E18" r:id="rId15" display="mailto:diptikanta.tripathy@harman.com" xr:uid="{B40C2DE9-D2A1-486F-A904-11AB91D54E65}"/>
-    <hyperlink ref="E19" r:id="rId16" display="mailto:deeksha.mongia2@harman.com" xr:uid="{1F15A93F-1F9D-40B1-A9FB-E56774027606}"/>
-    <hyperlink ref="E20" r:id="rId17" display="mailto:priya.ramesh@harman.com" xr:uid="{91279DA6-7AFD-4717-8C66-E094BEF1F1D6}"/>
-    <hyperlink ref="E21" r:id="rId18" display="mailto:vivek.patel@harman.com" xr:uid="{4B5775DA-CC52-4910-ADDD-8FA648697316}"/>
-    <hyperlink ref="E22" r:id="rId19" display="mailto:rahul.nigam2@harman.com" xr:uid="{96BB3D08-E4E2-4D0D-84A1-E3E57E790B93}"/>
-    <hyperlink ref="E23" r:id="rId20" display="mailto:neha.nema@harman.com" xr:uid="{1A0B205A-AE11-4E0F-82D2-084052A30E1F}"/>
+    <hyperlink ref="E8" r:id="rId4" display="mailto:gayatri.behera@harman.com" xr:uid="{21679528-AA71-4DE8-A4C0-D26B371344C7}"/>
+    <hyperlink ref="E9" r:id="rId5" display="mailto:kamran.siddiqui@harman.com" xr:uid="{B4354F16-B160-42FD-90B0-773FFAFA69F9}"/>
+    <hyperlink ref="E11" r:id="rId6" display="mailto:lalitha.saripalli@harman.com" xr:uid="{03B684BE-B201-4FAE-B650-8FE522DBB3A6}"/>
+    <hyperlink ref="E13" r:id="rId7" display="mailto:megha.kesharwani@harman.com" xr:uid="{11BC7E09-4E5B-4D32-84CC-8DC44E062A95}"/>
+    <hyperlink ref="E14" r:id="rId8" display="mailto:vaishnavi.ballal@harman.com" xr:uid="{C2A05FE7-4633-4420-92C8-D7E30C037435}"/>
+    <hyperlink ref="E15" r:id="rId9" display="mailto:rasmita.parida@harman.com" xr:uid="{2EC03D2C-4EB5-420F-A2AE-1CEBFA499E3E}"/>
+    <hyperlink ref="E16" r:id="rId10" display="mailto:varsha.gadekar@harman.com" xr:uid="{F317EFCD-459E-4968-8854-69713133520F}"/>
+    <hyperlink ref="E17" r:id="rId11" display="mailto:shunmuga.priya@harman.com" xr:uid="{735A5AAF-2FAB-4830-9EFE-E842143C12DD}"/>
+    <hyperlink ref="E18" r:id="rId12" display="mailto:sunkara.hussain@harman.com" xr:uid="{D8618987-6C7D-4B82-AC18-995F3E744827}"/>
+    <hyperlink ref="E19" r:id="rId13" display="mailto:hruthkarsha.ds@harman.com" xr:uid="{FC493C81-C249-4752-8703-861C7E251077}"/>
+    <hyperlink ref="E20" r:id="rId14" display="mailto:harshitha.v@harman.com" xr:uid="{DE50E738-2396-40D7-8B9C-ABCE851B9A6D}"/>
+    <hyperlink ref="E7" r:id="rId15" display="mailto:deeksha.mongia2@harman.com" xr:uid="{1F15A93F-1F9D-40B1-A9FB-E56774027606}"/>
+    <hyperlink ref="E10" r:id="rId16" display="mailto:priya.ramesh@harman.com" xr:uid="{91279DA6-7AFD-4717-8C66-E094BEF1F1D6}"/>
+    <hyperlink ref="E12" r:id="rId17" display="mailto:vivek.patel@harman.com" xr:uid="{4B5775DA-CC52-4910-ADDD-8FA648697316}"/>
+    <hyperlink ref="E21" r:id="rId18" display="mailto:rahul.nigam2@harman.com" xr:uid="{96BB3D08-E4E2-4D0D-84A1-E3E57E790B93}"/>
+    <hyperlink ref="E22" r:id="rId19" display="mailto:neha.nema@harman.com" xr:uid="{1A0B205A-AE11-4E0F-82D2-084052A30E1F}"/>
+    <hyperlink ref="E23" r:id="rId20" display="mailto:diptikanta.tripathy@harman.com" xr:uid="{3E39E4E0-F52D-499C-AFE6-94791F3D1E73}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
